--- a/artfynd/A 38908-2024 artfynd.xlsx
+++ b/artfynd/A 38908-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,6 +921,139 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118973124</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57201</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100096</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pandion haliaetus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stäholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>561721</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6594823</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Munktorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På bo.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Ekelund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Staffan Ekelund, Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38908-2024 artfynd.xlsx
+++ b/artfynd/A 38908-2024 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>118973124</v>
       </c>
       <c r="B4" t="n">
-        <v>57201</v>
+        <v>57209</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 38908-2024 artfynd.xlsx
+++ b/artfynd/A 38908-2024 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>118973138</v>
       </c>
       <c r="B3" t="n">
-        <v>57877</v>
+        <v>57882</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 38908-2024 artfynd.xlsx
+++ b/artfynd/A 38908-2024 artfynd.xlsx
@@ -817,11 +817,6 @@
       <c r="E3" t="n">
         <v>102995</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Buskskvätta</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Saxicola rubetra</t>

--- a/artfynd/A 38908-2024 artfynd.xlsx
+++ b/artfynd/A 38908-2024 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>118973138</v>
       </c>
       <c r="B3" t="n">
-        <v>57882</v>
+        <v>57886</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,6 +816,11 @@
       </c>
       <c r="E3" t="n">
         <v>102995</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
